--- a/experiment/Wavlet_bestx4/Test/results-Urban100/Urban100.xlsx
+++ b/experiment/Wavlet_bestx4/Test/results-Urban100/Urban100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.35</v>
+        <v>27.45</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7594</v>
+        <v>0.7631</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.36</v>
+        <v>26.54</v>
       </c>
       <c r="C3" t="n">
-        <v>0.802</v>
+        <v>0.8098</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.71</v>
+        <v>23.83</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6743</v>
+        <v>0.6821</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.86</v>
+        <v>23.29</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8125</v>
+        <v>0.8259</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.28</v>
+        <v>27.65</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9379</v>
+        <v>0.9419</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.35</v>
+        <v>22.36</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6163</v>
+        <v>0.6182</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29.3</v>
+        <v>29.38</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8551</v>
+        <v>0.8571</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.34</v>
+        <v>21.37</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6445</v>
+        <v>0.6483</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>33.45</v>
+        <v>33.64</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9171</v>
+        <v>0.9212</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26.82</v>
+        <v>26.97</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8777</v>
+        <v>0.8817</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17.68</v>
+        <v>17.79</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7739</v>
+        <v>0.7799</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23.71</v>
+        <v>23.66</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7184</v>
+        <v>0.7207</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29.1</v>
+        <v>29.24</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8223</v>
+        <v>0.8290999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22.28</v>
+        <v>22.34</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6761</v>
+        <v>0.6818</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25.73</v>
+        <v>25.87</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7229</v>
+        <v>0.7274</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29.92</v>
+        <v>30.13</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9094</v>
+        <v>0.9115</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25.46</v>
+        <v>25.58</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8157</v>
+        <v>0.8204</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>26.3</v>
+        <v>26.34</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7093</v>
+        <v>0.7117</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21.77</v>
+        <v>21.89</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7978</v>
+        <v>0.8024</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.01</v>
+        <v>22.1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7084</v>
+        <v>0.7141999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29.62</v>
+        <v>29.72</v>
       </c>
       <c r="C22" t="n">
-        <v>0.781</v>
+        <v>0.7838000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25.97</v>
+        <v>26.02</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7528</v>
+        <v>0.7562</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>29.94</v>
+        <v>29.97</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9061</v>
+        <v>0.9084</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>20.04</v>
+        <v>20.01</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6379</v>
+        <v>0.6395</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>31.09</v>
+        <v>31.51</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8884</v>
+        <v>0.8941</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27.56</v>
+        <v>27.8</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6879</v>
+        <v>0.6938</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28.14</v>
+        <v>28.25</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7907</v>
+        <v>0.7936</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31.05</v>
+        <v>31.2</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8683999999999999</v>
+        <v>0.8718</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>26.43</v>
+        <v>26.77</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8486</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>24.11</v>
+        <v>24.28</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7827</v>
+        <v>0.7926</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>24.01</v>
+        <v>24.1</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7763</v>
+        <v>0.7815</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>28.74</v>
+        <v>28.91</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8434</v>
+        <v>0.8473000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>26.8</v>
+        <v>26.98</v>
       </c>
       <c r="C34" t="n">
-        <v>0.781</v>
+        <v>0.7914</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>22.89</v>
+        <v>22.98</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5775</v>
+        <v>0.5817</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>28.34</v>
+        <v>28.49</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8555</v>
+        <v>0.8598</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>28.59</v>
+        <v>28.71</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8809</v>
+        <v>0.8835</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26.33</v>
+        <v>26.41</v>
       </c>
       <c r="C38" t="n">
-        <v>0.7931</v>
+        <v>0.7969000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>26.94</v>
+        <v>27.03</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6728</v>
+        <v>0.6788999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>22.7</v>
+        <v>22.86</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7249</v>
+        <v>0.7339</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26.59</v>
+        <v>27.08</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9245</v>
+        <v>0.9307</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25.65</v>
+        <v>25.68</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8633999999999999</v>
+        <v>0.8662</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>28.56</v>
+        <v>28.7</v>
       </c>
       <c r="C43" t="n">
-        <v>0.8763</v>
+        <v>0.881</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>30.43</v>
+        <v>31.28</v>
       </c>
       <c r="C44" t="n">
-        <v>0.9208</v>
+        <v>0.9249000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31.49</v>
+        <v>31.7</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8596</v>
+        <v>0.861</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24.06</v>
+        <v>24.3</v>
       </c>
       <c r="C46" t="n">
-        <v>0.7113</v>
+        <v>0.7193000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>23.52</v>
+        <v>23.55</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7488</v>
+        <v>0.7514999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>21.75</v>
+        <v>21.82</v>
       </c>
       <c r="C48" t="n">
-        <v>0.7554</v>
+        <v>0.7627</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>20.16</v>
+        <v>20.28</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8017</v>
+        <v>0.8079</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>23.16</v>
+        <v>23.31</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7335</v>
+        <v>0.7402</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25.15</v>
+        <v>25.22</v>
       </c>
       <c r="C51" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.7631</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="C52" t="n">
-        <v>0.8356</v>
+        <v>0.8398</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>28.13</v>
+        <v>28.45</v>
       </c>
       <c r="C53" t="n">
-        <v>0.8893</v>
+        <v>0.8962</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>22.13</v>
+        <v>22.27</v>
       </c>
       <c r="C54" t="n">
-        <v>0.7138</v>
+        <v>0.7227</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>21.04</v>
+        <v>21.11</v>
       </c>
       <c r="C55" t="n">
-        <v>0.6371</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>31.84</v>
+        <v>31.87</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9328</v>
+        <v>0.9298</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>24.68</v>
+        <v>24.8</v>
       </c>
       <c r="C57" t="n">
-        <v>0.7664</v>
+        <v>0.7731</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>30.27</v>
+        <v>30.49</v>
       </c>
       <c r="C58" t="n">
-        <v>0.8808</v>
+        <v>0.8848</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25.35</v>
+        <v>25.57</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8449</v>
+        <v>0.8515</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>21.89</v>
+        <v>21.9</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7498</v>
+        <v>0.7514</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>22.36</v>
+        <v>22.44</v>
       </c>
       <c r="C61" t="n">
-        <v>0.552</v>
+        <v>0.5584</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>24.55</v>
+        <v>24.59</v>
       </c>
       <c r="C62" t="n">
-        <v>0.7423</v>
+        <v>0.7467</v>
       </c>
     </row>
     <row r="63">
@@ -1248,7 +1248,7 @@
         <v>21.66</v>
       </c>
       <c r="C63" t="n">
-        <v>0.79</v>
+        <v>0.7965</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>22.14</v>
+        <v>22.24</v>
       </c>
       <c r="C64" t="n">
-        <v>0.611</v>
+        <v>0.6143999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>26.36</v>
+        <v>26.48</v>
       </c>
       <c r="C65" t="n">
-        <v>0.7744</v>
+        <v>0.7794</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>25.28</v>
+        <v>25.38</v>
       </c>
       <c r="C66" t="n">
-        <v>0.7147</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="C67" t="n">
-        <v>0.64</v>
+        <v>0.6431</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>19.62</v>
+        <v>19.73</v>
       </c>
       <c r="C68" t="n">
-        <v>0.8614000000000001</v>
+        <v>0.8658</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>30.14</v>
+        <v>30.16</v>
       </c>
       <c r="C69" t="n">
-        <v>0.8753</v>
+        <v>0.8781</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>24.6</v>
+        <v>24.65</v>
       </c>
       <c r="C70" t="n">
-        <v>0.7435</v>
+        <v>0.7452</v>
       </c>
     </row>
     <row r="71">
@@ -1352,7 +1352,7 @@
         <v>22.08</v>
       </c>
       <c r="C71" t="n">
-        <v>0.5898</v>
+        <v>0.5908</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>27.61</v>
+        <v>27.76</v>
       </c>
       <c r="C72" t="n">
-        <v>0.6494</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>19.85</v>
+        <v>20.08</v>
       </c>
       <c r="C73" t="n">
-        <v>0.7984</v>
+        <v>0.8082</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>20.09</v>
+        <v>20.12</v>
       </c>
       <c r="C74" t="n">
-        <v>0.5507</v>
+        <v>0.555</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>23.49</v>
+        <v>23.6</v>
       </c>
       <c r="C75" t="n">
-        <v>0.6831</v>
+        <v>0.6924</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>31.08</v>
+        <v>31.34</v>
       </c>
       <c r="C76" t="n">
-        <v>0.8754999999999999</v>
+        <v>0.8792</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>22.57</v>
+        <v>22.45</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.7139</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>22.65</v>
+        <v>22.69</v>
       </c>
       <c r="C78" t="n">
-        <v>0.6667</v>
+        <v>0.6701</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>27.15</v>
+        <v>27</v>
       </c>
       <c r="C79" t="n">
-        <v>0.7625999999999999</v>
+        <v>0.7637</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>25.18</v>
+        <v>25.27</v>
       </c>
       <c r="C80" t="n">
-        <v>0.6833</v>
+        <v>0.6887</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>35.18</v>
+        <v>35.34</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9455</v>
+        <v>0.9485</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>35.74</v>
+        <v>36.11</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9617</v>
+        <v>0.964</v>
       </c>
     </row>
     <row r="83">
@@ -1508,7 +1508,7 @@
         <v>32.57</v>
       </c>
       <c r="C83" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9383</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>22.08</v>
+        <v>22.17</v>
       </c>
       <c r="C84" t="n">
-        <v>0.6836</v>
+        <v>0.6904</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>28.45</v>
+        <v>28.51</v>
       </c>
       <c r="C85" t="n">
-        <v>0.8025</v>
+        <v>0.8052</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>27.72</v>
+        <v>28</v>
       </c>
       <c r="C86" t="n">
-        <v>0.8895</v>
+        <v>0.8952</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>30.26</v>
+        <v>30.28</v>
       </c>
       <c r="C87" t="n">
-        <v>0.883</v>
+        <v>0.8819</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>27.14</v>
+        <v>27.37</v>
       </c>
       <c r="C88" t="n">
-        <v>0.8679</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>19.8</v>
+        <v>19.87</v>
       </c>
       <c r="C89" t="n">
-        <v>0.5554</v>
+        <v>0.5629999999999999</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>26.64</v>
+        <v>26.67</v>
       </c>
       <c r="C90" t="n">
-        <v>0.7092000000000001</v>
+        <v>0.7109</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>36.64</v>
+        <v>37.11</v>
       </c>
       <c r="C91" t="n">
-        <v>0.9679</v>
+        <v>0.9708</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>23.76</v>
+        <v>23.86</v>
       </c>
       <c r="C92" t="n">
-        <v>0.6599</v>
+        <v>0.6664</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>18.48</v>
+        <v>18.54</v>
       </c>
       <c r="C93" t="n">
-        <v>0.6237</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>28.35</v>
+        <v>28.12</v>
       </c>
       <c r="C94" t="n">
-        <v>0.9166</v>
+        <v>0.9172</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>26.97</v>
+        <v>27.09</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7752</v>
+        <v>0.7803</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>19.98</v>
+        <v>20.02</v>
       </c>
       <c r="C96" t="n">
-        <v>0.4244</v>
+        <v>0.4316</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>24.64</v>
+        <v>24.49</v>
       </c>
       <c r="C97" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.8493000000000001</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>24.64</v>
+        <v>24.76</v>
       </c>
       <c r="C98" t="n">
-        <v>0.7486</v>
+        <v>0.7544</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>20.54</v>
+        <v>20.61</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5137</v>
+        <v>0.5192</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>25.21</v>
+        <v>25.42</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.7793</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>25.72</v>
+        <v>25.93</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7288</v>
+        <v>0.7372</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>25.68</v>
+        <v>25.81</v>
       </c>
       <c r="C102" t="n">
-        <v>0.7709</v>
+        <v>0.7756999999999999</v>
       </c>
     </row>
   </sheetData>
